--- a/pdf/annexe-bts.xlsx
+++ b/pdf/annexe-bts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33658\Desktop\PortfolioAZiz\pdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535BE265-AB54-43FE-8533-220E40E8C966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9655517-B5B3-4BC3-8B1C-C88D2059C50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,15 @@
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="BTS_SERVICES_INFORMATIQUES_AUX_ORGANISATIONS">'Tableau de synthèse Épreuve E4'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$45</definedName>
+    <definedName name="BTS_SERVICES_INFORMATIQUES_AUX_ORGANISATIONS">'Tableau de synthèse Épreuve E4'!$A$1:$H$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="101716" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="53">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -99,9 +99,6 @@
 (intitulé et liste des documents et productions associés)</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
@@ -117,144 +114,94 @@
     <t>Centre de formation : Lycée Turgot</t>
   </si>
   <si>
-    <t>01/09/2024 au 11/12/2024</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
-    <t>Organisation à l'aide d'un diagramme de Gantt</t>
-  </si>
-  <si>
-    <t>25/11/2024 au 11/12/2024</t>
-  </si>
-  <si>
-    <t>Installation d'un serveur Apache pour déployer un site en ligne</t>
-  </si>
-  <si>
-    <t>Déploiement d'un service SSH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création et gestion d'une base de donnée SQL </t>
-  </si>
-  <si>
-    <t>01/10/2024 au 12/12/2024</t>
-  </si>
-  <si>
-    <t>24/09/2024 au 12/12/2024</t>
+    <t>X SISR</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://itzazizo.github.io/PortfolioAziz/</t>
+  </si>
+  <si>
+    <t>NOM et prénom : BENYAMINA-HOUARI Aziz</t>
+  </si>
+  <si>
+    <t>02/12/2024 au 24/01/2025</t>
+  </si>
+  <si>
+    <t>25/11/24 au 11/12/24</t>
+  </si>
+  <si>
+    <t>24/09/24 au 12/12/24</t>
+  </si>
+  <si>
+    <t>10/2025 au 11/2025</t>
+  </si>
+  <si>
+    <t>sept.-25</t>
+  </si>
+  <si>
+    <t>TP : Services Réseau : Paramétrage DHCP, DNS et NAT.</t>
+  </si>
+  <si>
+    <t>TP : Sécurité pfSense : Installation, configuration NAT et règles de filtrage LAN/WAN.</t>
+  </si>
+  <si>
+    <t>TP : Supervision : Inventaire automatisé via déploiement d'agents GLPI par GPO.</t>
+  </si>
+  <si>
+    <t>Déploiement Système (WDS) : Capture d'image Windows 11 et déploiement PXE.</t>
+  </si>
+  <si>
+    <t>Segmentation réseau : Configuration de switch Enterasys (VLAN et SSH).</t>
+  </si>
+  <si>
+    <t>Gestion de parc : Installation d'imprimantes HP et inventaire matériel GLPI.</t>
+  </si>
+  <si>
+    <t>Maintenance ToIP : Support et mise en service de terminaux IP Avaya et Ascom.</t>
+  </si>
+  <si>
+    <t>N° candidat : 2541473544</t>
+  </si>
+  <si>
+    <t>04/01/25 au 23/4/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Création d'un portfolio accessible sur internet (HTML, CSS, JS).</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
   </si>
   <si>
     <t>x</t>
   </si>
   <si>
-    <t>Réalisation d'un site web (Projet jeu Devine le Nombre)
-(Javascript, html, css)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réalisation d'un cahier des charges 
-</t>
-  </si>
-  <si>
-    <t>X SISR</t>
-  </si>
-  <si>
-    <t>Configuration des routeurs et switches avec segmentation via VLAN.</t>
-  </si>
-  <si>
-    <t>Paramétrage des services réseau essentiels tels que DHCP, DNS et NAT.</t>
-  </si>
-  <si>
-    <t>Déploiement d’un serveur de messagerie sous Linux avec Postfix et Dovecot, intégré à un Active Directory.</t>
-  </si>
-  <si>
-    <t>Configuration d’un Active Directory sous Windows pour la gestion centralisée des utilisateurs et des accès.</t>
-  </si>
-  <si>
-    <t>Hébergement d’un site web sur une machine Debian pour la communication et la gestion des services en ligne.</t>
-  </si>
-  <si>
-    <t>Déploiement de l’outil Kanboard pour la gestion des projets au sein d’une petite structure.</t>
-  </si>
-  <si>
-    <t>Durcissement et audit de sécurité d'un serveur Debian 13 avec Lynis, UFW et Fail2Ban.</t>
-  </si>
-  <si>
-    <t>Mise en place d'une infrastructure Docker sécurisée avec segmentation réseau et sauvegardes automatisées.</t>
-  </si>
-  <si>
-    <t>Déploiement d'une stack d'authentification sur Kubernetes avec Helm et résolution d'incidents Ingress.</t>
-  </si>
-  <si>
-    <t>Sécurisation d'un cluster K3s par le chiffrement au repos et la gestion des secrets via Sealed Secrets.</t>
-  </si>
-  <si>
-    <t>Installation d'un serveur GitLab CE sécurisé par un VPN WireGuard et automatisation des sauvegardes.</t>
-  </si>
-  <si>
-    <t>Création de guides de sensibilisation sur la gestion des mots de passe, le MFA et le phishing</t>
-  </si>
-  <si>
-    <t>Installation d'Auditd et AIDE pour surveiller en temps réel les modifications critiques du système de fichiers</t>
-  </si>
-  <si>
-    <t>Gestion du parc d'impression : Installation et configuration d'imprimantes HP sur serveur d'impression avec gestion des pilotes et des ports TCP/IP.</t>
-  </si>
-  <si>
-    <t>Maintenance de la téléphonie IP : Support et mise en service de terminaux IP Avaya et Ascom au sein d'une infrastructure IPABX hospitalière.</t>
-  </si>
-  <si>
-    <t>Segmentation réseau (Switch) : Configuration d'un commutateur Enterasys incluant la création de VLAN (Backup), l'activation du SSH et la sécurisation des accès.</t>
-  </si>
-  <si>
-    <t>Déploiement système (WDS) : Préparation et capture d'une image de référence Windows 11 pour automatiser le déploiement des postes via le réseau (PXE).</t>
-  </si>
-  <si>
-    <t>Inventaire automatisé (GLPI) : Déploiement de l'agent GLPI sur les postes clients pour assurer la remontée automatique de l'inventaire matériel et logiciel.</t>
-  </si>
-  <si>
-    <t>Optimisation du stockage LVM et migration de VM critique (Cluster Proxmox</t>
-  </si>
-  <si>
-    <t>Configuration des routeurs et switches avec segmentation par VLAN pour isoler les flux.</t>
-  </si>
-  <si>
-    <t>Projet Mairie : Segmentation réseau et sécurisation des accès Wi-Fi/Filaires par VLAN pour isoler les services administratifs et publics.</t>
-  </si>
-  <si>
-    <t>Activation et configuration des journaux d'audit (audit logs) pour tracer chaque action effectuée sur le cluster K3s.</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio : https://itzazizo.github.io/PortfolioAziz/</t>
-  </si>
-  <si>
-    <t>NOM et prénom : BENYAMINA-HOUARI Aziz</t>
-  </si>
-  <si>
-    <t>10/09/2024 au 11/09/2024</t>
-  </si>
-  <si>
-    <t>06/09/2024 au 06/12/2024</t>
-  </si>
-  <si>
-    <t>Création infrastructure réseau ( Packet tracer)</t>
-  </si>
-  <si>
-    <t>10/2025-11/2025</t>
-  </si>
-  <si>
-    <t>Installation et configuration d'un système IDS/IPS pour la détection et le blocage proactif d'intrusions sur le réseau.</t>
-  </si>
-  <si>
-    <t>Planification des activités et suivi des ressources à l'aide d'un diagramme de Gantt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Installation d'un pare-feu pfSense, configuration du NAT sortant et mise en place de règles de filtrage LAN/WAN.</t>
-  </si>
-  <si>
-    <t>02/12/2024 au 24/01/2025</t>
-  </si>
-  <si>
-    <t>Mise en place de l'inventaire automatisé via le déploiement d'agents GLPI par GPO  sur un Active Directory.</t>
+    <t>Projet 1 : Site Web : Étude des besoins et réalisation du jeu "Devine le Nombre" (JS, HTML, CSS).</t>
+  </si>
+  <si>
+    <t>Projet 2  : Messagerie Linux : Étude technique et déploiement Postfix/Dovecot intégré à un AD.</t>
+  </si>
+  <si>
+    <t>Projet 3: Projet Mairie : Cahier des charges et segmentation Wi-Fi/Filaires par VLAN.</t>
+  </si>
+  <si>
+    <t>Veille Technologique (Outils de veille, flux RSS, exploitation de ressources numériques)</t>
+  </si>
+  <si>
+    <t>2024-2026</t>
+  </si>
+  <si>
+    <t>Infrastructure DevOps : Mise en place Docker, Cluster K3s et déploiement via Helm.</t>
+  </si>
+  <si>
+    <t>Audit &amp; Durcissement Sécurité : Audit Debian 13 avec Lynis et protection via Fail2Ban/UFW.</t>
+  </si>
+  <si>
+    <t>Outils Collaboratifs Sécurisés : Installation GitLab CE et accès sécurisé via VPN WireGuard.</t>
+  </si>
+  <si>
+    <t>Gouvernance &amp; Surveillance : Installation Auditd/AIDE et sensibilisation au Phishing/MFA.</t>
   </si>
 </sst>
 </file>
@@ -264,7 +211,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -322,11 +269,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="28"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial1"/>
@@ -341,11 +283,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -381,7 +318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -482,21 +419,6 @@
         <color theme="2" tint="-0.749992370372631"/>
       </top>
       <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
@@ -794,26 +716,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -821,19 +730,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -842,112 +745,90 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -957,19 +838,22 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="7" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1281,7 +1165,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ89"/>
+  <dimension ref="A1:AQ71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
@@ -1292,123 +1176,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="29"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:43" ht="39.9" customHeight="1">
-      <c r="A3" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="37"/>
+      <c r="A3" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="21"/>
+      <c r="H3" s="27"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1">
-      <c r="A4" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="8" t="s">
+      <c r="A4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A5" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="53"/>
+      <c r="A5" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1">
-      <c r="A7" s="45"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="11" t="s">
+      <c r="A7" s="35"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="10" t="s">
         <v>14</v>
       </c>
       <c r="I7"/>
@@ -1448,16 +1332,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="72" customHeight="1" thickBot="1">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="48"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1495,19 +1379,23 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A9" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>61</v>
+      <c r="A9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="F9" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="13"/>
+        <v>23</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="H9" s="14"/>
       <c r="I9"/>
       <c r="J9"/>
@@ -1546,24 +1434,26 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="18"/>
+      <c r="A10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="14"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1601,22 +1491,26 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18" t="s">
-        <v>25</v>
-      </c>
+      <c r="A11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="14"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1654,22 +1548,22 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
+      <c r="A12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="14"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1707,24 +1601,22 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17" t="s">
+      <c r="A13" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="18"/>
+      <c r="B13" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="14"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1762,22 +1654,24 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A14" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
+      <c r="A14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="44">
+        <v>46054</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="14"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1815,40 +1709,38 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="18"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-      <c r="R15"/>
-      <c r="S15"/>
-      <c r="T15"/>
-      <c r="U15"/>
-      <c r="V15"/>
-      <c r="W15"/>
-      <c r="X15"/>
-      <c r="Y15"/>
-      <c r="Z15"/>
+      <c r="A15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
@@ -1867,23 +1759,21 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="21.6" thickBot="1">
-      <c r="A16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="52.2" customHeight="1" thickBot="1">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="14" t="s">
+        <v>43</v>
+      </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1921,28 +1811,16 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>25</v>
-      </c>
+      <c r="A17" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="30"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1980,26 +1858,22 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>25</v>
-      </c>
+      <c r="A18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="11"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -2036,23 +1910,21 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A19" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="18"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="28.2" thickBot="1">
+      <c r="A19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="11"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2090,26 +1962,22 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A20" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18" t="s">
-        <v>25</v>
-      </c>
+      <c r="A20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="11"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2147,24 +2015,20 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="17"/>
-      <c r="H21" s="18"/>
+      <c r="A21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="11"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2202,28 +2066,16 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A22" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>33</v>
-      </c>
+      <c r="A22" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="33"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2260,23 +2112,23 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A23" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="24">
-        <v>45901</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="18"/>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
+      <c r="A23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2313,852 +2165,77 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A24" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="25">
-        <v>46327</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
-      <c r="I24"/>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24"/>
-      <c r="O24"/>
-      <c r="P24"/>
-      <c r="Q24"/>
-      <c r="R24"/>
-      <c r="S24"/>
-      <c r="T24"/>
-      <c r="U24"/>
-      <c r="V24"/>
-      <c r="W24"/>
-      <c r="X24"/>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24"/>
-      <c r="AB24"/>
-      <c r="AC24"/>
-      <c r="AD24"/>
-      <c r="AE24"/>
-      <c r="AF24"/>
-      <c r="AG24"/>
-      <c r="AH24"/>
-      <c r="AI24"/>
-      <c r="AJ24"/>
-      <c r="AK24"/>
-      <c r="AL24"/>
-      <c r="AM24"/>
-      <c r="AN24"/>
-      <c r="AO24"/>
-      <c r="AP24"/>
-      <c r="AQ24"/>
-    </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A25" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="24">
-        <v>46054</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="18"/>
-      <c r="I25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
-      <c r="N25"/>
-      <c r="O25"/>
-      <c r="P25"/>
-      <c r="Q25"/>
-      <c r="R25"/>
-      <c r="S25"/>
-      <c r="T25"/>
-      <c r="U25"/>
-      <c r="V25"/>
-      <c r="W25"/>
-      <c r="X25"/>
-      <c r="Y25"/>
-      <c r="Z25"/>
-      <c r="AA25"/>
-      <c r="AB25"/>
-      <c r="AC25"/>
-      <c r="AD25"/>
-      <c r="AE25"/>
-      <c r="AF25"/>
-      <c r="AG25"/>
-      <c r="AH25"/>
-      <c r="AI25"/>
-      <c r="AJ25"/>
-      <c r="AK25"/>
-      <c r="AL25"/>
-      <c r="AM25"/>
-      <c r="AN25"/>
-      <c r="AO25"/>
-      <c r="AP25"/>
-      <c r="AQ25"/>
-    </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="24">
-        <v>45901</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-      <c r="R26"/>
-      <c r="S26"/>
-      <c r="T26"/>
-      <c r="U26"/>
-      <c r="V26"/>
-      <c r="W26"/>
-      <c r="X26"/>
-      <c r="Y26"/>
-      <c r="Z26"/>
-      <c r="AA26"/>
-      <c r="AB26"/>
-      <c r="AC26"/>
-      <c r="AD26"/>
-      <c r="AE26"/>
-      <c r="AF26"/>
-      <c r="AG26"/>
-      <c r="AH26"/>
-      <c r="AI26"/>
-      <c r="AJ26"/>
-      <c r="AK26"/>
-      <c r="AL26"/>
-      <c r="AM26"/>
-      <c r="AN26"/>
-      <c r="AO26"/>
-      <c r="AP26"/>
-      <c r="AQ26"/>
-    </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A27" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="24">
-        <v>46054</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="18"/>
-      <c r="I27"/>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27"/>
-      <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27"/>
-      <c r="P27"/>
-      <c r="Q27"/>
-      <c r="R27"/>
-      <c r="S27"/>
-      <c r="T27"/>
-      <c r="U27"/>
-      <c r="V27"/>
-      <c r="W27"/>
-      <c r="X27"/>
-      <c r="Y27"/>
-      <c r="Z27"/>
-      <c r="AA27"/>
-      <c r="AB27"/>
-      <c r="AC27"/>
-      <c r="AD27"/>
-      <c r="AE27"/>
-      <c r="AF27"/>
-      <c r="AG27"/>
-      <c r="AH27"/>
-      <c r="AI27"/>
-      <c r="AJ27"/>
-      <c r="AK27"/>
-      <c r="AL27"/>
-      <c r="AM27"/>
-      <c r="AN27"/>
-      <c r="AO27"/>
-      <c r="AP27"/>
-      <c r="AQ27"/>
-    </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="24">
-        <v>46054</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="H28" s="18"/>
-      <c r="I28"/>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28"/>
-      <c r="R28"/>
-      <c r="S28"/>
-      <c r="T28"/>
-      <c r="U28"/>
-      <c r="V28"/>
-      <c r="W28"/>
-      <c r="X28"/>
-      <c r="Y28"/>
-      <c r="Z28"/>
-      <c r="AA28"/>
-      <c r="AB28"/>
-      <c r="AC28"/>
-      <c r="AD28"/>
-      <c r="AE28"/>
-      <c r="AF28"/>
-      <c r="AG28"/>
-      <c r="AH28"/>
-      <c r="AI28"/>
-      <c r="AJ28"/>
-      <c r="AK28"/>
-      <c r="AL28"/>
-      <c r="AM28"/>
-      <c r="AN28"/>
-      <c r="AO28"/>
-      <c r="AP28"/>
-      <c r="AQ28"/>
-    </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39" customHeight="1" thickBot="1">
-      <c r="A29" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" s="18"/>
-      <c r="I29"/>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29"/>
-      <c r="M29"/>
-      <c r="N29"/>
-      <c r="O29"/>
-      <c r="P29"/>
-      <c r="Q29"/>
-      <c r="R29"/>
-      <c r="S29"/>
-      <c r="T29"/>
-      <c r="U29"/>
-      <c r="V29"/>
-      <c r="W29"/>
-      <c r="X29"/>
-      <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29"/>
-      <c r="AB29"/>
-      <c r="AC29"/>
-      <c r="AD29"/>
-      <c r="AE29"/>
-      <c r="AF29"/>
-      <c r="AG29"/>
-      <c r="AH29"/>
-      <c r="AI29"/>
-      <c r="AJ29"/>
-      <c r="AK29"/>
-      <c r="AL29"/>
-      <c r="AM29"/>
-      <c r="AN29"/>
-      <c r="AO29"/>
-      <c r="AP29"/>
-      <c r="AQ29"/>
-    </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A30" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="40"/>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="R30"/>
-      <c r="S30"/>
-      <c r="T30"/>
-      <c r="U30"/>
-      <c r="V30"/>
-      <c r="W30"/>
-      <c r="X30"/>
-      <c r="Y30"/>
-      <c r="Z30"/>
-      <c r="AA30"/>
-      <c r="AB30"/>
-      <c r="AC30"/>
-      <c r="AD30"/>
-      <c r="AE30"/>
-      <c r="AF30"/>
-      <c r="AG30"/>
-      <c r="AH30"/>
-      <c r="AI30"/>
-      <c r="AJ30"/>
-      <c r="AK30"/>
-      <c r="AL30"/>
-      <c r="AM30"/>
-      <c r="AN30"/>
-      <c r="AO30"/>
-      <c r="AP30"/>
-      <c r="AQ30"/>
-    </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A31" s="6" t="s">
+    <row r="24" spans="1:43" customFormat="1" ht="41.4" customHeight="1" thickBot="1">
+      <c r="A24" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="15"/>
-      <c r="I31"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31"/>
-      <c r="P31"/>
-      <c r="Q31"/>
-      <c r="R31"/>
-      <c r="S31"/>
-      <c r="T31"/>
-      <c r="U31"/>
-      <c r="V31"/>
-      <c r="W31"/>
-      <c r="X31"/>
-      <c r="Y31"/>
-      <c r="Z31"/>
-      <c r="AA31"/>
-      <c r="AB31"/>
-      <c r="AC31"/>
-      <c r="AD31"/>
-      <c r="AE31"/>
-      <c r="AF31"/>
-      <c r="AG31"/>
-      <c r="AH31"/>
-      <c r="AI31"/>
-      <c r="AJ31"/>
-      <c r="AK31"/>
-      <c r="AL31"/>
-      <c r="AM31"/>
-      <c r="AN31"/>
-      <c r="AO31"/>
-      <c r="AP31"/>
-      <c r="AQ31"/>
-    </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="42" thickBot="1">
-      <c r="A32" s="6" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:43" customFormat="1" ht="36.6" customHeight="1" thickBot="1">
+      <c r="A25" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H32" s="15"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-      <c r="P32"/>
-      <c r="Q32"/>
-      <c r="R32"/>
-      <c r="S32"/>
-      <c r="T32"/>
-      <c r="U32"/>
-      <c r="V32"/>
-      <c r="W32"/>
-      <c r="X32"/>
-      <c r="Y32"/>
-      <c r="Z32"/>
-      <c r="AA32"/>
-      <c r="AB32"/>
-      <c r="AC32"/>
-      <c r="AD32"/>
-      <c r="AE32"/>
-      <c r="AF32"/>
-      <c r="AG32"/>
-      <c r="AH32"/>
-      <c r="AI32"/>
-      <c r="AJ32"/>
-      <c r="AK32"/>
-      <c r="AL32"/>
-      <c r="AM32"/>
-      <c r="AN32"/>
-      <c r="AO32"/>
-      <c r="AP32"/>
-      <c r="AQ32"/>
-    </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A33" s="6" t="s">
+      <c r="B25" s="18"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:43" customFormat="1" ht="37.200000000000003" customHeight="1" thickBot="1">
+      <c r="A26" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="15"/>
-      <c r="I33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33"/>
-      <c r="R33"/>
-      <c r="S33"/>
-      <c r="T33"/>
-      <c r="U33"/>
-      <c r="V33"/>
-      <c r="W33"/>
-      <c r="X33"/>
-      <c r="Y33"/>
-      <c r="Z33"/>
-      <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33"/>
-      <c r="AE33"/>
-      <c r="AF33"/>
-      <c r="AG33"/>
-      <c r="AH33"/>
-      <c r="AI33"/>
-      <c r="AJ33"/>
-      <c r="AK33"/>
-      <c r="AL33"/>
-      <c r="AM33"/>
-      <c r="AN33"/>
-      <c r="AO33"/>
-      <c r="AP33"/>
-      <c r="AQ33"/>
-    </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A34" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H34" s="15"/>
-      <c r="I34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
-      <c r="R34"/>
-      <c r="S34"/>
-      <c r="T34"/>
-      <c r="U34"/>
-      <c r="V34"/>
-      <c r="W34"/>
-      <c r="X34"/>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34"/>
-      <c r="AB34"/>
-      <c r="AC34"/>
-      <c r="AD34"/>
-      <c r="AE34"/>
-      <c r="AF34"/>
-      <c r="AG34"/>
-      <c r="AH34"/>
-      <c r="AI34"/>
-      <c r="AJ34"/>
-      <c r="AK34"/>
-      <c r="AL34"/>
-      <c r="AM34"/>
-      <c r="AN34"/>
-      <c r="AO34"/>
-      <c r="AP34"/>
-      <c r="AQ34"/>
-    </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A35" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="15"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-    </row>
-    <row r="36" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1">
-      <c r="A36" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36" s="42"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="43"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36"/>
-      <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36"/>
-      <c r="P36"/>
-      <c r="Q36"/>
-      <c r="R36"/>
-      <c r="S36"/>
-      <c r="T36"/>
-      <c r="U36"/>
-      <c r="V36"/>
-      <c r="W36"/>
-      <c r="X36"/>
-      <c r="Y36"/>
-      <c r="Z36"/>
-      <c r="AA36"/>
-      <c r="AB36"/>
-      <c r="AC36"/>
-      <c r="AD36"/>
-      <c r="AE36"/>
-      <c r="AF36"/>
-      <c r="AG36"/>
-      <c r="AH36"/>
-      <c r="AI36"/>
-      <c r="AJ36"/>
-      <c r="AK36"/>
-      <c r="AL36"/>
-      <c r="AM36"/>
-      <c r="AN36"/>
-      <c r="AO36"/>
-      <c r="AP36"/>
-      <c r="AQ36"/>
-    </row>
-    <row r="37" spans="1:43" s="2" customFormat="1" ht="28.2" customHeight="1" thickBot="1">
-      <c r="A37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="I37"/>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37"/>
-      <c r="M37"/>
-      <c r="N37"/>
-      <c r="O37"/>
-      <c r="P37"/>
-      <c r="Q37"/>
-      <c r="R37"/>
-      <c r="S37"/>
-      <c r="T37"/>
-      <c r="U37"/>
-      <c r="V37"/>
-      <c r="W37"/>
-      <c r="X37"/>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37"/>
-      <c r="AB37"/>
-      <c r="AC37"/>
-      <c r="AD37"/>
-      <c r="AE37"/>
-      <c r="AF37"/>
-      <c r="AG37"/>
-      <c r="AH37"/>
-      <c r="AI37"/>
-      <c r="AJ37"/>
-      <c r="AK37"/>
-      <c r="AL37"/>
-      <c r="AM37"/>
-      <c r="AN37"/>
-      <c r="AO37"/>
-      <c r="AP37"/>
-      <c r="AQ37"/>
-    </row>
-    <row r="38" spans="1:43" customFormat="1" ht="41.4" customHeight="1" thickBot="1">
-      <c r="A38" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="27"/>
-      <c r="C38" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:43" customFormat="1" ht="36.6" customHeight="1" thickBot="1">
-      <c r="A39" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H39" s="16"/>
-    </row>
-    <row r="40" spans="1:43" customFormat="1" ht="37.200000000000003" customHeight="1" thickBot="1">
-      <c r="A40" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="41" spans="1:43" customFormat="1" ht="43.8" customHeight="1" thickBot="1">
-      <c r="A41" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="27"/>
-      <c r="C41" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H41" s="16"/>
-    </row>
-    <row r="42" spans="1:43" customFormat="1" ht="52.2" customHeight="1" thickBot="1">
-      <c r="A42" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H42" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:43" customFormat="1" ht="33" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:43" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A44" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" s="28"/>
-      <c r="C44" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="H44" s="23"/>
-    </row>
-    <row r="45" spans="1:43" customFormat="1" ht="16.2" thickBot="1">
-      <c r="B45" s="20"/>
-    </row>
-    <row r="46" spans="1:43" customFormat="1"/>
-    <row r="47" spans="1:43" customFormat="1"/>
-    <row r="48" spans="1:43" customFormat="1"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:43" customFormat="1" ht="43.8" customHeight="1" thickBot="1">
+      <c r="A27" s="11"/>
+      <c r="B27" s="18"/>
+    </row>
+    <row r="28" spans="1:43" customFormat="1"/>
+    <row r="29" spans="1:43" customFormat="1"/>
+    <row r="30" spans="1:43" customFormat="1"/>
+    <row r="31" spans="1:43" customFormat="1"/>
+    <row r="32" spans="1:43" customFormat="1"/>
+    <row r="33" customFormat="1"/>
+    <row r="34" customFormat="1"/>
+    <row r="35" customFormat="1"/>
+    <row r="36" customFormat="1"/>
+    <row r="37" customFormat="1"/>
+    <row r="38" customFormat="1"/>
+    <row r="39" customFormat="1"/>
+    <row r="40" customFormat="1"/>
+    <row r="41" customFormat="1"/>
+    <row r="42" customFormat="1"/>
+    <row r="43" customFormat="1"/>
+    <row r="44" customFormat="1"/>
+    <row r="45" customFormat="1"/>
+    <row r="46" customFormat="1"/>
+    <row r="47" customFormat="1"/>
+    <row r="48" customFormat="1"/>
     <row r="49" customFormat="1"/>
     <row r="50" customFormat="1"/>
     <row r="51" customFormat="1"/>
@@ -3175,61 +2252,43 @@
     <row r="62" customFormat="1"/>
     <row r="63" customFormat="1"/>
     <row r="64" customFormat="1"/>
-    <row r="65" customFormat="1"/>
-    <row r="66" customFormat="1"/>
-    <row r="67" customFormat="1"/>
-    <row r="68" customFormat="1"/>
-    <row r="69" customFormat="1"/>
-    <row r="70" customFormat="1"/>
-    <row r="71" customFormat="1"/>
-    <row r="72" customFormat="1"/>
-    <row r="73" customFormat="1"/>
-    <row r="74" customFormat="1"/>
-    <row r="75" customFormat="1"/>
-    <row r="76" customFormat="1"/>
-    <row r="77" customFormat="1"/>
-    <row r="78" customFormat="1"/>
-    <row r="79" customFormat="1"/>
-    <row r="80" customFormat="1"/>
-    <row r="81" spans="1:8" customFormat="1"/>
-    <row r="82" spans="1:8" customFormat="1"/>
-    <row r="83" spans="1:8" customFormat="1"/>
-    <row r="84" spans="1:8">
-      <c r="A84"/>
-      <c r="B84"/>
-      <c r="C84"/>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86"/>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87"/>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88"/>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89"/>
+    <row r="65" spans="1:8" customFormat="1"/>
+    <row r="66" spans="1:8">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69"/>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B37:B44"/>
-    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="B18:B21"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
